--- a/temp-peyroll-form/Overall-payroll.xlsx
+++ b/temp-peyroll-form/Overall-payroll.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Congty\thienphumut\test\thienphumut-hr-backend\temp-peyroll-form\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B242D8-7522-4DB3-AB5D-5AC08B627718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A40317A0-00FE-4E2A-B281-318B004D3ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22046" yWindow="-163" windowWidth="22149" windowHeight="13200" xr2:uid="{E83EA0EC-134B-4F25-9614-1B9231720E55}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{E83EA0EC-134B-4F25-9614-1B9231720E55}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="68">
   <si>
     <t>DƯ BỎ ĐI</t>
   </si>
@@ -222,7 +222,7 @@
     <t>B</t>
   </si>
   <si>
-    <t>Tháng 02 /2026</t>
+    <t>Tháng 03 /2026</t>
   </si>
   <si>
     <t>01818</t>
@@ -368,7 +368,7 @@
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -425,7 +425,6 @@
     <xf numFmtId="49" fontId="5" fillId="6" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -744,72 +743,72 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3985D44-62BA-4E83-9C5B-043893CE1D86}">
   <dimension ref="A1:BK7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.9" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.75" style="22" customWidth="1"/>
-    <col min="2" max="2" width="10.75" style="17" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" style="22" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" style="17" customWidth="1"/>
     <col min="3" max="3" width="9" style="17"/>
-    <col min="4" max="4" width="28.08203125" style="17" customWidth="1"/>
-    <col min="5" max="5" width="10.75" style="17" customWidth="1"/>
-    <col min="6" max="6" width="17.75" style="23" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="18" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.25" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.0703125" style="17" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" style="17" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" style="23" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="18" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.2109375" style="17" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" style="17" customWidth="1"/>
-    <col min="10" max="10" width="12.75" style="17" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" style="17" customWidth="1"/>
-    <col min="12" max="12" width="8.25" style="17" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.75" style="23" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="17" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" style="17" customWidth="1"/>
+    <col min="11" max="11" width="12.35546875" style="17" customWidth="1"/>
+    <col min="12" max="12" width="8.2109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.7109375" style="17" customWidth="1"/>
     <col min="15" max="15" width="13.5" style="23" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.25" style="17" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.08203125" style="17" customWidth="1"/>
-    <col min="18" max="18" width="8.25" style="17" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.25" style="17" customWidth="1"/>
-    <col min="20" max="20" width="8.08203125" style="17" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.33203125" style="17" customWidth="1"/>
+    <col min="16" max="16" width="8.2109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.0703125" style="17" customWidth="1"/>
+    <col min="18" max="18" width="8.2109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.2109375" style="17" customWidth="1"/>
+    <col min="20" max="20" width="8.0703125" style="17" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.35546875" style="17" customWidth="1"/>
     <col min="22" max="23" width="13.5" style="23" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.75" style="23" customWidth="1"/>
-    <col min="25" max="25" width="13.33203125" style="17" customWidth="1"/>
-    <col min="26" max="26" width="12.08203125" style="17" customWidth="1"/>
-    <col min="27" max="27" width="10.33203125" style="17" customWidth="1"/>
-    <col min="28" max="28" width="8.08203125" style="17" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.08203125" style="17" customWidth="1"/>
-    <col min="30" max="30" width="8.08203125" style="17" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="10.08203125" style="17" customWidth="1"/>
-    <col min="32" max="32" width="10.58203125" style="17" customWidth="1"/>
-    <col min="33" max="33" width="13.58203125" style="17" customWidth="1"/>
-    <col min="34" max="35" width="12.75" style="17" customWidth="1"/>
-    <col min="36" max="36" width="10.33203125" style="17" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="23" customWidth="1"/>
+    <col min="25" max="25" width="13.35546875" style="17" customWidth="1"/>
+    <col min="26" max="26" width="12.0703125" style="17" customWidth="1"/>
+    <col min="27" max="27" width="10.35546875" style="17" customWidth="1"/>
+    <col min="28" max="28" width="8.0703125" style="17" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.0703125" style="17" customWidth="1"/>
+    <col min="30" max="30" width="8.0703125" style="17" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="10.0703125" style="17" customWidth="1"/>
+    <col min="32" max="32" width="10.5703125" style="17" customWidth="1"/>
+    <col min="33" max="33" width="13.5703125" style="17" customWidth="1"/>
+    <col min="34" max="35" width="12.7109375" style="17" customWidth="1"/>
+    <col min="36" max="36" width="10.35546875" style="17" customWidth="1"/>
     <col min="37" max="37" width="13.5" style="17" customWidth="1"/>
-    <col min="38" max="38" width="10.58203125" style="17" customWidth="1"/>
-    <col min="39" max="39" width="12.33203125" style="17" customWidth="1"/>
-    <col min="40" max="40" width="8.25" style="17" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.33203125" style="17" customWidth="1"/>
-    <col min="42" max="42" width="8.25" style="17" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="10.5703125" style="17" customWidth="1"/>
+    <col min="39" max="39" width="12.35546875" style="17" customWidth="1"/>
+    <col min="40" max="40" width="8.2109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.35546875" style="17" customWidth="1"/>
+    <col min="42" max="42" width="8.2109375" style="17" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="16.5" style="17" customWidth="1"/>
-    <col min="44" max="44" width="10.83203125" style="17" customWidth="1"/>
-    <col min="45" max="45" width="8.08203125" style="17" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="8.25" style="17" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="18.75" style="17" customWidth="1"/>
-    <col min="48" max="48" width="14.75" style="23" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="10.85546875" style="17" customWidth="1"/>
+    <col min="45" max="45" width="8.0703125" style="17" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="8.2109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="18.7109375" style="17" customWidth="1"/>
+    <col min="48" max="48" width="14.7109375" style="23" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="13.5" style="17" customWidth="1"/>
     <col min="50" max="50" width="16" style="18" customWidth="1"/>
     <col min="51" max="51" width="13.5" style="18" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="11.25" style="17" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="13.83203125" style="17" customWidth="1"/>
-    <col min="54" max="54" width="13.33203125" style="17" customWidth="1"/>
-    <col min="55" max="55" width="10.75" style="17" customWidth="1"/>
-    <col min="56" max="56" width="11.08203125" style="17" customWidth="1"/>
+    <col min="52" max="52" width="11.2109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="13.85546875" style="17" customWidth="1"/>
+    <col min="54" max="54" width="13.35546875" style="17" customWidth="1"/>
+    <col min="55" max="55" width="10.7109375" style="17" customWidth="1"/>
+    <col min="56" max="56" width="11.0703125" style="17" customWidth="1"/>
     <col min="57" max="57" width="10.5" style="17" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="18.58203125" style="18" customWidth="1"/>
-    <col min="59" max="59" width="14.75" style="18" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="18.5703125" style="18" customWidth="1"/>
+    <col min="59" max="59" width="14.7109375" style="18" bestFit="1" customWidth="1"/>
     <col min="60" max="61" width="9" style="17"/>
-    <col min="62" max="62" width="10.58203125" style="17" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="9.83203125" style="17" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="10.5703125" style="17" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="9.85546875" style="17" bestFit="1" customWidth="1"/>
     <col min="64" max="16384" width="9" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:63" s="2" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:63" s="2" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>65</v>
@@ -871,7 +870,7 @@
       <c r="BF1" s="3"/>
       <c r="BG1" s="3"/>
     </row>
-    <row r="2" spans="1:63" s="16" customFormat="1" ht="65" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:63" s="16" customFormat="1" ht="62.15" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -1050,9 +1049,9 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:63" ht="18" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:63" ht="18" x14ac:dyDescent="0.45">
       <c r="A3" s="21" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>61</v>
@@ -1079,10 +1078,10 @@
         <v>1415576.923076923</v>
       </c>
       <c r="J3" s="20">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" s="20">
-        <v>360000</v>
+        <v>0</v>
       </c>
       <c r="L3" s="20">
         <v>12.1</v>
@@ -1091,70 +1090,56 @@
         <v>3425696</v>
       </c>
       <c r="N3" s="20">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O3" s="20">
-        <v>360900</v>
+        <v>0</v>
       </c>
       <c r="P3" s="20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="20">
-        <v>260000</v>
+        <v>0</v>
       </c>
       <c r="R3" s="20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S3" s="20">
-        <v>340000</v>
-      </c>
-      <c r="T3" s="20">
-        <v>12</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T3" s="20"/>
       <c r="U3" s="20">
-        <v>360100</v>
+        <v>0</v>
       </c>
       <c r="V3" s="20">
-        <v>129999</v>
+        <v>0</v>
       </c>
       <c r="W3" s="20">
-        <v>240000</v>
+        <v>0</v>
       </c>
       <c r="X3" s="20">
-        <v>210000</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="20">
         <v>297380.76923076925</v>
       </c>
       <c r="Z3" s="20">
-        <v>210000</v>
+        <v>0</v>
       </c>
       <c r="AA3" s="20">
-        <v>430000</v>
-      </c>
-      <c r="AB3" s="17">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AC3" s="20">
-        <v>120000</v>
-      </c>
-      <c r="AD3" s="17">
-        <v>3</v>
-      </c>
-      <c r="AE3" s="17">
-        <v>241999</v>
-      </c>
-      <c r="AF3" s="17">
-        <v>129433</v>
+        <v>0</v>
       </c>
       <c r="AG3" s="20">
-        <v>120555</v>
+        <v>0</v>
       </c>
       <c r="AH3" s="20">
-        <v>999999</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="20">
-        <v>129444</v>
+        <v>0</v>
       </c>
       <c r="AK3" s="20">
         <v>0</v>
@@ -1163,26 +1148,17 @@
         <v>0</v>
       </c>
       <c r="AN3" s="20">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AO3" s="20">
-        <v>350111</v>
+        <v>0</v>
       </c>
       <c r="AP3" s="20">
         <v>1</v>
       </c>
-      <c r="AQ3" s="17">
-        <v>132222</v>
-      </c>
-      <c r="AR3" s="17">
-        <v>8</v>
-      </c>
       <c r="AS3" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="AT3" s="24">
-        <v>0.3</v>
-      </c>
       <c r="AU3" s="20">
         <v>744615.38461538462</v>
       </c>
@@ -1199,19 +1175,19 @@
         <v>840000</v>
       </c>
       <c r="AZ3" s="20">
-        <v>320000</v>
+        <v>0</v>
       </c>
       <c r="BB3" s="20">
-        <v>312222</v>
+        <v>0</v>
       </c>
       <c r="BC3" s="20">
-        <v>312222</v>
+        <v>0</v>
       </c>
       <c r="BD3" s="20">
-        <v>312222</v>
+        <v>0</v>
       </c>
       <c r="BE3" s="20">
-        <v>312222</v>
+        <v>0</v>
       </c>
       <c r="BF3" s="18">
         <v>880000</v>
@@ -1226,9 +1202,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:63" ht="18" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:63" ht="18" x14ac:dyDescent="0.45">
       <c r="A4" s="21" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>61</v>
@@ -1379,7 +1355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:63" ht="18" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:63" ht="18" x14ac:dyDescent="0.45">
       <c r="A5" s="21" t="s">
         <v>67</v>
       </c>
@@ -1532,8 +1508,160 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:63" ht="20.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="1:63" ht="20.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="1:63" ht="18" x14ac:dyDescent="0.45">
+      <c r="A6" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="20">
+        <v>10000000</v>
+      </c>
+      <c r="G6" s="20">
+        <v>7361000</v>
+      </c>
+      <c r="H6" s="20">
+        <v>5</v>
+      </c>
+      <c r="I6" s="20">
+        <v>1415576.923076923</v>
+      </c>
+      <c r="J6" s="20">
+        <v>0</v>
+      </c>
+      <c r="K6" s="20">
+        <v>0</v>
+      </c>
+      <c r="L6" s="20">
+        <v>12.1</v>
+      </c>
+      <c r="M6" s="20">
+        <v>3425696</v>
+      </c>
+      <c r="N6" s="20">
+        <v>0</v>
+      </c>
+      <c r="O6" s="20">
+        <v>0</v>
+      </c>
+      <c r="P6" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="20">
+        <v>0</v>
+      </c>
+      <c r="R6" s="20">
+        <v>0</v>
+      </c>
+      <c r="S6" s="20">
+        <v>0</v>
+      </c>
+      <c r="T6" s="20"/>
+      <c r="U6" s="20">
+        <v>0</v>
+      </c>
+      <c r="V6" s="20">
+        <v>0</v>
+      </c>
+      <c r="W6" s="20">
+        <v>0</v>
+      </c>
+      <c r="X6" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="20">
+        <v>297380.76923076925</v>
+      </c>
+      <c r="Z6" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="20">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="20">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="20">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="20">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="20">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="20">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="20">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="20">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="20">
+        <v>0</v>
+      </c>
+      <c r="AP6" s="20">
+        <v>1</v>
+      </c>
+      <c r="AS6" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU6" s="20">
+        <v>744615.38461538462</v>
+      </c>
+      <c r="AV6" s="20">
+        <v>5883269.076923077</v>
+      </c>
+      <c r="AW6" s="20">
+        <v>8000000</v>
+      </c>
+      <c r="AX6" s="18">
+        <v>40000</v>
+      </c>
+      <c r="AY6" s="18">
+        <v>840000</v>
+      </c>
+      <c r="AZ6" s="20">
+        <v>0</v>
+      </c>
+      <c r="BB6" s="20">
+        <v>0</v>
+      </c>
+      <c r="BC6" s="20">
+        <v>0</v>
+      </c>
+      <c r="BD6" s="20">
+        <v>0</v>
+      </c>
+      <c r="BE6" s="20">
+        <v>0</v>
+      </c>
+      <c r="BF6" s="18">
+        <v>880000</v>
+      </c>
+      <c r="BG6" s="20">
+        <v>5003269.076923077</v>
+      </c>
+      <c r="BJ6" s="20">
+        <v>5003269.076923077</v>
+      </c>
+      <c r="BK6" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:63" ht="20.25" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/temp-peyroll-form/Overall-payroll.xlsx
+++ b/temp-peyroll-form/Overall-payroll.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Congty\thienphumut\test\thienphumut-hr-backend\temp-peyroll-form\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A40317A0-00FE-4E2A-B281-318B004D3ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2120F649-21DB-4088-A5DB-AAD03FE2D385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{E83EA0EC-134B-4F25-9614-1B9231720E55}"/>
   </bookViews>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="68">
-  <si>
-    <t>DƯ BỎ ĐI</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="66">
   <si>
     <t>Mã NV</t>
   </si>
@@ -183,9 +180,6 @@
     <t>Truy thu BHYT</t>
   </si>
   <si>
-    <t>Bảo hiểm</t>
-  </si>
-  <si>
     <t>Thuế TNCN</t>
   </si>
   <si>
@@ -204,43 +198,45 @@
     <t xml:space="preserve">Thực lãnh </t>
   </si>
   <si>
+    <t>Tháng 02 /2026</t>
+  </si>
+  <si>
+    <t>Phép năm còn lại của năm</t>
+  </si>
+  <si>
+    <t>Tiền phép năm trong năm</t>
+  </si>
+  <si>
+    <t>chỉnh sửa</t>
+  </si>
+  <si>
     <t>01115</t>
   </si>
   <si>
-    <t>01/10/2025</t>
-  </si>
-  <si>
-    <t>6530734238</t>
-  </si>
-  <si>
     <t>IT</t>
   </si>
   <si>
-    <t>ĐOÀN NGUYỄN MINH ĐĂNG</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>Tháng 03 /2026</t>
-  </si>
-  <si>
-    <t>01818</t>
-  </si>
-  <si>
-    <t>03636</t>
+    <t>Đoàn Nguyễn Minh Đăng</t>
+  </si>
+  <si>
+    <t>15/01/2026</t>
+  </si>
+  <si>
+    <t>Giỏi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0\ _₫_-;\-* #,##0\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="[$VND]\ #,##0"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.0\ _₫_-;\-* #,##0.0\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -274,7 +270,18 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3913DD"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -284,8 +291,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -322,6 +334,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -347,28 +371,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -418,21 +436,75 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="7" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="8" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Comma 18 2" xfId="2" xr:uid="{9E7F5F4A-4B6B-4A21-8B15-7677E4732828}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="3" xr:uid="{4CE527C1-C229-4199-A14D-31D50D89CC1A}"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -742,76 +814,76 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3985D44-62BA-4E83-9C5B-043893CE1D86}">
-  <dimension ref="A1:BK7"/>
+  <dimension ref="A1:BO6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.9" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" style="22" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" style="17" customWidth="1"/>
-    <col min="3" max="3" width="9" style="17"/>
-    <col min="4" max="4" width="28.0703125" style="17" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" style="17" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" style="23" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="18" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.2109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11" style="17" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" style="17" customWidth="1"/>
-    <col min="11" max="11" width="12.35546875" style="17" customWidth="1"/>
-    <col min="12" max="12" width="8.2109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="23" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.7109375" style="17" customWidth="1"/>
-    <col min="15" max="15" width="13.5" style="23" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.2109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.0703125" style="17" customWidth="1"/>
-    <col min="18" max="18" width="8.2109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.2109375" style="17" customWidth="1"/>
-    <col min="20" max="20" width="8.0703125" style="17" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.35546875" style="17" customWidth="1"/>
-    <col min="22" max="23" width="13.5" style="23" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="23" customWidth="1"/>
-    <col min="25" max="25" width="13.35546875" style="17" customWidth="1"/>
-    <col min="26" max="26" width="12.0703125" style="17" customWidth="1"/>
-    <col min="27" max="27" width="10.35546875" style="17" customWidth="1"/>
-    <col min="28" max="28" width="8.0703125" style="17" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.0703125" style="17" customWidth="1"/>
-    <col min="30" max="30" width="8.0703125" style="17" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="10.0703125" style="17" customWidth="1"/>
-    <col min="32" max="32" width="10.5703125" style="17" customWidth="1"/>
-    <col min="33" max="33" width="13.5703125" style="17" customWidth="1"/>
-    <col min="34" max="35" width="12.7109375" style="17" customWidth="1"/>
-    <col min="36" max="36" width="10.35546875" style="17" customWidth="1"/>
-    <col min="37" max="37" width="13.5" style="17" customWidth="1"/>
-    <col min="38" max="38" width="10.5703125" style="17" customWidth="1"/>
-    <col min="39" max="39" width="12.35546875" style="17" customWidth="1"/>
-    <col min="40" max="40" width="8.2109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.35546875" style="17" customWidth="1"/>
-    <col min="42" max="42" width="8.2109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="16.5" style="17" customWidth="1"/>
-    <col min="44" max="44" width="10.85546875" style="17" customWidth="1"/>
-    <col min="45" max="45" width="8.0703125" style="17" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="8.2109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="18.7109375" style="17" customWidth="1"/>
-    <col min="48" max="48" width="14.7109375" style="23" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="13.5" style="17" customWidth="1"/>
-    <col min="50" max="50" width="16" style="18" customWidth="1"/>
-    <col min="51" max="51" width="13.5" style="18" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="11.2109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="13.85546875" style="17" customWidth="1"/>
-    <col min="54" max="54" width="13.35546875" style="17" customWidth="1"/>
-    <col min="55" max="55" width="10.7109375" style="17" customWidth="1"/>
-    <col min="56" max="56" width="11.0703125" style="17" customWidth="1"/>
-    <col min="57" max="57" width="10.5" style="17" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="18.5703125" style="18" customWidth="1"/>
-    <col min="59" max="59" width="14.7109375" style="18" bestFit="1" customWidth="1"/>
-    <col min="60" max="61" width="9" style="17"/>
-    <col min="62" max="62" width="10.5703125" style="17" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="9.85546875" style="17" bestFit="1" customWidth="1"/>
-    <col min="64" max="16384" width="9" style="17"/>
+    <col min="1" max="1" width="13.7109375" style="30" customWidth="1"/>
+    <col min="2" max="2" width="16.0703125" style="26" customWidth="1"/>
+    <col min="3" max="3" width="9" style="26"/>
+    <col min="4" max="4" width="28.140625" style="26" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" style="26" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" style="31" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.2109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" style="26" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" style="26" customWidth="1"/>
+    <col min="11" max="11" width="12.35546875" style="26" customWidth="1"/>
+    <col min="12" max="12" width="8.2109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.7109375" style="26" customWidth="1"/>
+    <col min="15" max="15" width="13.5" style="31" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.2109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.140625" style="26" customWidth="1"/>
+    <col min="18" max="18" width="8.2109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.2109375" style="26" customWidth="1"/>
+    <col min="20" max="20" width="8.140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.35546875" style="26" customWidth="1"/>
+    <col min="22" max="23" width="13.5" style="31" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="31" customWidth="1"/>
+    <col min="25" max="25" width="13.35546875" style="26" customWidth="1"/>
+    <col min="26" max="26" width="12.140625" style="26" customWidth="1"/>
+    <col min="27" max="27" width="10.35546875" style="26" customWidth="1"/>
+    <col min="28" max="28" width="8.140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.140625" style="26" customWidth="1"/>
+    <col min="30" max="30" width="8.140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="10.140625" style="26" customWidth="1"/>
+    <col min="32" max="32" width="10.640625" style="26" customWidth="1"/>
+    <col min="33" max="33" width="13.640625" style="26" customWidth="1"/>
+    <col min="34" max="35" width="12.7109375" style="26" customWidth="1"/>
+    <col min="36" max="36" width="10.35546875" style="26" customWidth="1"/>
+    <col min="37" max="37" width="13.5" style="26" customWidth="1"/>
+    <col min="38" max="38" width="10.640625" style="26" customWidth="1"/>
+    <col min="39" max="39" width="12.35546875" style="26" customWidth="1"/>
+    <col min="40" max="41" width="8.2109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.35546875" style="26" customWidth="1"/>
+    <col min="43" max="43" width="8.2109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="8.2109375" style="26" customWidth="1"/>
+    <col min="45" max="45" width="16.5" style="26" customWidth="1"/>
+    <col min="46" max="46" width="10.85546875" style="26" customWidth="1"/>
+    <col min="47" max="47" width="8.140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="8.2109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="18.7109375" style="26" customWidth="1"/>
+    <col min="50" max="50" width="14.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.5" style="26" customWidth="1"/>
+    <col min="52" max="52" width="16" style="27" customWidth="1"/>
+    <col min="53" max="53" width="13.5" style="27" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="11.2109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="13.35546875" style="26" customWidth="1"/>
+    <col min="56" max="56" width="10.7109375" style="26" customWidth="1"/>
+    <col min="57" max="57" width="11.140625" style="26" customWidth="1"/>
+    <col min="58" max="58" width="12.92578125" style="26" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="18.640625" style="27" customWidth="1"/>
+    <col min="60" max="60" width="14.7109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="61" max="62" width="9" style="26"/>
+    <col min="63" max="63" width="10.640625" style="26" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="9.85546875" style="26" bestFit="1" customWidth="1"/>
+    <col min="65" max="16384" width="9" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:63" s="2" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:67" s="2" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
@@ -847,822 +919,462 @@
       <c r="AK1" s="4"/>
       <c r="AL1" s="4"/>
       <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
-      <c r="AP1" s="4"/>
-      <c r="AQ1" s="4"/>
-      <c r="AR1" s="4"/>
-      <c r="AS1" s="4"/>
+      <c r="AN1" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="AO1" s="33"/>
+      <c r="AP1" s="33"/>
+      <c r="AQ1" s="33"/>
+      <c r="AR1" s="33"/>
+      <c r="AS1" s="33"/>
       <c r="AT1" s="4"/>
       <c r="AU1" s="4"/>
-      <c r="AV1" s="3"/>
+      <c r="AV1" s="4"/>
       <c r="AW1" s="4"/>
       <c r="AX1" s="3"/>
-      <c r="AY1" s="3"/>
-      <c r="AZ1" s="4"/>
-      <c r="BA1" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="AY1" s="4"/>
+      <c r="AZ1" s="3"/>
+      <c r="BA1" s="3"/>
       <c r="BB1" s="4"/>
       <c r="BC1" s="4"/>
       <c r="BD1" s="4"/>
       <c r="BE1" s="4"/>
-      <c r="BF1" s="3"/>
+      <c r="BF1" s="4"/>
       <c r="BG1" s="3"/>
+      <c r="BH1" s="3"/>
     </row>
-    <row r="2" spans="1:63" s="16" customFormat="1" ht="62.15" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:67" s="16" customFormat="1" ht="62.15" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="G2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="I2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="J2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="K2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="L2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="M2" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="N2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="O2" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="P2" s="6" t="s">
+      <c r="Q2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="9" t="s">
+      <c r="R2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="S2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="9" t="s">
+      <c r="T2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="6" t="s">
+      <c r="U2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="U2" s="9" t="s">
+      <c r="V2" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="V2" s="11" t="s">
+      <c r="W2" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="W2" s="11" t="s">
+      <c r="X2" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="X2" s="11" t="s">
+      <c r="Y2" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="Y2" s="9" t="s">
+      <c r="Z2" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="Z2" s="9" t="s">
+      <c r="AA2" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="AA2" s="9" t="s">
+      <c r="AB2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AB2" s="6" t="s">
+      <c r="AC2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="AC2" s="9" t="s">
+      <c r="AD2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="AD2" s="6" t="s">
+      <c r="AE2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="AE2" s="6" t="s">
+      <c r="AF2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AF2" s="6" t="s">
+      <c r="AG2" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="AG2" s="9" t="s">
+      <c r="AH2" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="AH2" s="9" t="s">
+      <c r="AI2" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="AI2" s="9" t="s">
+      <c r="AJ2" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="AJ2" s="9" t="s">
+      <c r="AK2" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="AK2" s="9" t="s">
+      <c r="AL2" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="AL2" s="9" t="s">
+      <c r="AM2" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="AM2" s="6" t="s">
+      <c r="AN2" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="AN2" s="6" t="s">
+      <c r="AO2" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP2" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="AO2" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP2" s="12" t="s">
+      <c r="AQ2" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="AR2" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="AS2" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="AQ2" s="9" t="s">
+      <c r="AT2" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="AR2" s="6" t="s">
+      <c r="AU2" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="AS2" s="6" t="s">
+      <c r="AV2" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="AT2" s="6" t="s">
+      <c r="AW2" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="AU2" s="9" t="s">
+      <c r="AX2" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="AV2" s="7" t="s">
+      <c r="AY2" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="AW2" s="12" t="s">
+      <c r="AZ2" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="AX2" s="13" t="s">
+      <c r="BA2" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="AY2" s="13" t="s">
+      <c r="BB2" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="AZ2" s="14" t="s">
+      <c r="BC2" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="BA2" s="14" t="s">
+      <c r="BD2" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="BB2" s="14" t="s">
+      <c r="BE2" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="BC2" s="14" t="s">
+      <c r="BF2" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="BD2" s="14" t="s">
+      <c r="BG2" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="BE2" s="14" t="s">
+      <c r="BH2" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="BF2" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="BG2" s="15" t="s">
-        <v>58</v>
-      </c>
     </row>
-    <row r="3" spans="1:63" ht="18" x14ac:dyDescent="0.45">
-      <c r="A3" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" s="17" t="s">
+    <row r="3" spans="1:67" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="34" t="s">
         <v>61</v>
+      </c>
+      <c r="B3" s="35">
+        <v>1932910012</v>
       </c>
       <c r="C3" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="17" t="s">
-        <v>60</v>
+      <c r="E3" s="19" t="s">
+        <v>64</v>
       </c>
       <c r="F3" s="20">
         <v>10000000</v>
       </c>
       <c r="G3" s="20">
-        <v>7361000</v>
-      </c>
-      <c r="H3" s="20">
+        <v>7000000</v>
+      </c>
+      <c r="H3" s="21">
+        <v>3</v>
+      </c>
+      <c r="I3" s="20">
+        <v>360000</v>
+      </c>
+      <c r="J3" s="21">
+        <v>2</v>
+      </c>
+      <c r="K3" s="20">
+        <v>180000</v>
+      </c>
+      <c r="L3" s="21">
+        <v>27</v>
+      </c>
+      <c r="M3" s="20">
+        <v>8000000</v>
+      </c>
+      <c r="N3" s="21">
+        <v>1</v>
+      </c>
+      <c r="O3" s="20">
+        <v>120000</v>
+      </c>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="20"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="20"/>
+      <c r="T3" s="21">
+        <v>27</v>
+      </c>
+      <c r="U3" s="20">
+        <v>270000</v>
+      </c>
+      <c r="V3" s="20">
+        <v>60000</v>
+      </c>
+      <c r="W3" s="20">
+        <v>70000</v>
+      </c>
+      <c r="X3" s="20">
+        <v>80000</v>
+      </c>
+      <c r="Y3" s="20">
+        <v>90000</v>
+      </c>
+      <c r="Z3" s="20">
+        <v>100000</v>
+      </c>
+      <c r="AA3" s="20">
+        <v>110000</v>
+      </c>
+      <c r="AB3" s="22">
+        <v>2</v>
+      </c>
+      <c r="AC3" s="20">
+        <v>240000</v>
+      </c>
+      <c r="AD3" s="21">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="20">
+        <v>120000</v>
+      </c>
+      <c r="AF3" s="21">
+        <v>130000</v>
+      </c>
+      <c r="AG3" s="20">
+        <v>140000</v>
+      </c>
+      <c r="AH3" s="20">
+        <v>150000</v>
+      </c>
+      <c r="AI3" s="20">
+        <v>160000</v>
+      </c>
+      <c r="AJ3" s="21">
+        <v>170000</v>
+      </c>
+      <c r="AK3" s="20">
+        <v>180000</v>
+      </c>
+      <c r="AL3" s="20">
+        <v>190000</v>
+      </c>
+      <c r="AM3" s="20">
+        <v>200000</v>
+      </c>
+      <c r="AN3" s="21">
+        <v>3</v>
+      </c>
+      <c r="AO3" s="21">
         <v>5</v>
       </c>
-      <c r="I3" s="20">
-        <v>1415576.923076923</v>
-      </c>
-      <c r="J3" s="20">
-        <v>0</v>
-      </c>
-      <c r="K3" s="20">
-        <v>0</v>
-      </c>
-      <c r="L3" s="20">
-        <v>12.1</v>
-      </c>
-      <c r="M3" s="20">
-        <v>3425696</v>
-      </c>
-      <c r="N3" s="20">
-        <v>0</v>
-      </c>
-      <c r="O3" s="20">
-        <v>0</v>
-      </c>
-      <c r="P3" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="20">
-        <v>0</v>
-      </c>
-      <c r="R3" s="20">
-        <v>0</v>
-      </c>
-      <c r="S3" s="20">
-        <v>0</v>
-      </c>
-      <c r="T3" s="20"/>
-      <c r="U3" s="20">
-        <v>0</v>
-      </c>
-      <c r="V3" s="20">
-        <v>0</v>
-      </c>
-      <c r="W3" s="20">
-        <v>0</v>
-      </c>
-      <c r="X3" s="20">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="20">
-        <v>297380.76923076925</v>
-      </c>
-      <c r="Z3" s="20">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="20">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="20">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="20">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="20">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="20">
-        <v>0</v>
-      </c>
-      <c r="AK3" s="20">
-        <v>0</v>
-      </c>
-      <c r="AL3" s="20">
-        <v>0</v>
-      </c>
-      <c r="AN3" s="20">
-        <v>0</v>
-      </c>
-      <c r="AO3" s="20">
-        <v>0</v>
-      </c>
       <c r="AP3" s="20">
-        <v>1</v>
-      </c>
-      <c r="AS3" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="AU3" s="20">
-        <v>744615.38461538462</v>
-      </c>
-      <c r="AV3" s="20">
-        <v>5883269.076923077</v>
+        <v>360000</v>
+      </c>
+      <c r="AQ3" s="21">
+        <v>4</v>
+      </c>
+      <c r="AR3" s="21">
+        <v>420000</v>
+      </c>
+      <c r="AS3" s="20">
+        <v>360000</v>
+      </c>
+      <c r="AT3" s="23">
+        <v>9</v>
+      </c>
+      <c r="AU3" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="AV3" s="25">
+        <v>1.2</v>
       </c>
       <c r="AW3" s="20">
-        <v>8000000</v>
-      </c>
-      <c r="AX3" s="18">
+        <v>470000</v>
+      </c>
+      <c r="AX3" s="20">
+        <v>9200000</v>
+      </c>
+      <c r="AY3" s="20">
+        <v>210000</v>
+      </c>
+      <c r="AZ3" s="20">
+        <v>30000</v>
+      </c>
+      <c r="BA3" s="20">
         <v>40000</v>
       </c>
-      <c r="AY3" s="18">
-        <v>840000</v>
-      </c>
-      <c r="AZ3" s="20">
-        <v>0</v>
-      </c>
       <c r="BB3" s="20">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="BC3" s="20">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="BD3" s="20">
-        <v>0</v>
+        <v>3000000</v>
       </c>
       <c r="BE3" s="20">
-        <v>0</v>
-      </c>
-      <c r="BF3" s="18">
-        <v>880000</v>
+        <v>120000</v>
+      </c>
+      <c r="BF3" s="20">
+        <v>1100000</v>
       </c>
       <c r="BG3" s="20">
-        <v>5003269.076923077</v>
-      </c>
-      <c r="BJ3" s="20">
-        <v>5003269.076923077</v>
-      </c>
-      <c r="BK3" s="19">
-        <v>0</v>
-      </c>
+        <v>310000</v>
+      </c>
+      <c r="BH3" s="20">
+        <v>9360000</v>
+      </c>
+      <c r="BJ3" s="27"/>
+      <c r="BK3" s="27"/>
+      <c r="BL3" s="27"/>
+      <c r="BM3" s="28"/>
+      <c r="BN3" s="28"/>
+      <c r="BO3" s="29"/>
     </row>
-    <row r="4" spans="1:63" ht="18" x14ac:dyDescent="0.45">
-      <c r="A4" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" s="20">
-        <v>10000000</v>
-      </c>
-      <c r="G4" s="20">
-        <v>7361000</v>
-      </c>
-      <c r="H4" s="20">
-        <v>5</v>
-      </c>
-      <c r="I4" s="20">
-        <v>1415576.923076923</v>
-      </c>
-      <c r="J4" s="20">
-        <v>0</v>
-      </c>
-      <c r="K4" s="20">
-        <v>0</v>
-      </c>
-      <c r="L4" s="20">
-        <v>12.1</v>
-      </c>
-      <c r="M4" s="20">
-        <v>3425696</v>
-      </c>
-      <c r="N4" s="20">
-        <v>0</v>
-      </c>
-      <c r="O4" s="20">
-        <v>0</v>
-      </c>
-      <c r="P4" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="20">
-        <v>0</v>
-      </c>
-      <c r="R4" s="20">
-        <v>0</v>
-      </c>
-      <c r="S4" s="20">
-        <v>0</v>
-      </c>
-      <c r="T4" s="20"/>
-      <c r="U4" s="20">
-        <v>0</v>
-      </c>
-      <c r="V4" s="20">
-        <v>0</v>
-      </c>
-      <c r="W4" s="20">
-        <v>0</v>
-      </c>
-      <c r="X4" s="20">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="20">
-        <v>297380.76923076925</v>
-      </c>
-      <c r="Z4" s="20">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="20">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="20">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="20">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="20">
-        <v>0</v>
-      </c>
-      <c r="AI4" s="20">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="20">
-        <v>0</v>
-      </c>
-      <c r="AL4" s="20">
-        <v>0</v>
-      </c>
-      <c r="AN4" s="20">
-        <v>0</v>
-      </c>
-      <c r="AO4" s="20">
-        <v>0</v>
-      </c>
-      <c r="AP4" s="20">
-        <v>1</v>
-      </c>
-      <c r="AS4" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="AU4" s="20">
-        <v>744615.38461538462</v>
-      </c>
-      <c r="AV4" s="20">
-        <v>5883269.076923077</v>
-      </c>
-      <c r="AW4" s="20">
-        <v>8000000</v>
-      </c>
-      <c r="AX4" s="18">
-        <v>40000</v>
-      </c>
-      <c r="AY4" s="18">
-        <v>840000</v>
-      </c>
-      <c r="AZ4" s="20">
-        <v>0</v>
-      </c>
-      <c r="BB4" s="20">
-        <v>0</v>
-      </c>
-      <c r="BC4" s="20">
-        <v>0</v>
-      </c>
-      <c r="BD4" s="20">
-        <v>0</v>
-      </c>
-      <c r="BE4" s="20">
-        <v>0</v>
-      </c>
-      <c r="BF4" s="18">
-        <v>880000</v>
-      </c>
-      <c r="BG4" s="20">
-        <v>5003269.076923077</v>
-      </c>
-      <c r="BJ4" s="20">
-        <v>5003269.076923077</v>
-      </c>
-      <c r="BK4" s="19">
-        <v>0</v>
-      </c>
+    <row r="6" spans="1:67" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="36"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="36"/>
+      <c r="K6" s="37"/>
+      <c r="L6" s="36"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="37"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="37"/>
+      <c r="R6" s="36"/>
+      <c r="S6" s="36"/>
+      <c r="T6" s="36"/>
+      <c r="U6" s="37"/>
+      <c r="V6" s="37"/>
+      <c r="W6" s="37"/>
+      <c r="X6" s="37"/>
+      <c r="Y6" s="37"/>
+      <c r="Z6" s="37"/>
+      <c r="AA6" s="37"/>
+      <c r="AB6" s="36"/>
+      <c r="AC6" s="37"/>
+      <c r="AD6" s="36"/>
+      <c r="AE6" s="36"/>
+      <c r="AF6" s="37"/>
+      <c r="AG6" s="37"/>
+      <c r="AH6" s="37"/>
+      <c r="AI6" s="37"/>
+      <c r="AJ6" s="37"/>
+      <c r="AK6" s="37"/>
+      <c r="AL6" s="37"/>
+      <c r="AM6" s="37"/>
+      <c r="AN6" s="36"/>
+      <c r="AO6" s="36"/>
+      <c r="AP6" s="37"/>
+      <c r="AQ6" s="36"/>
+      <c r="AR6" s="37"/>
+      <c r="AS6" s="37"/>
+      <c r="AT6" s="36"/>
+      <c r="AU6" s="36"/>
+      <c r="AV6" s="38"/>
+      <c r="AW6" s="37"/>
+      <c r="AX6" s="37"/>
+      <c r="AY6" s="37"/>
+      <c r="AZ6" s="37"/>
+      <c r="BA6" s="37"/>
+      <c r="BB6" s="37"/>
+      <c r="BC6" s="37"/>
+      <c r="BD6" s="37"/>
+      <c r="BE6" s="37"/>
+      <c r="BF6" s="37"/>
+      <c r="BG6" s="37"/>
+      <c r="BH6" s="37"/>
     </row>
-    <row r="5" spans="1:63" ht="18" x14ac:dyDescent="0.45">
-      <c r="A5" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="F5" s="20">
-        <v>10000000</v>
-      </c>
-      <c r="G5" s="20">
-        <v>7361000</v>
-      </c>
-      <c r="H5" s="20">
-        <v>5</v>
-      </c>
-      <c r="I5" s="20">
-        <v>1415576.923076923</v>
-      </c>
-      <c r="J5" s="20">
-        <v>0</v>
-      </c>
-      <c r="K5" s="20">
-        <v>0</v>
-      </c>
-      <c r="L5" s="20">
-        <v>12.1</v>
-      </c>
-      <c r="M5" s="20">
-        <v>3425696</v>
-      </c>
-      <c r="N5" s="20">
-        <v>0</v>
-      </c>
-      <c r="O5" s="20">
-        <v>0</v>
-      </c>
-      <c r="P5" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="20">
-        <v>0</v>
-      </c>
-      <c r="R5" s="20">
-        <v>0</v>
-      </c>
-      <c r="S5" s="20">
-        <v>0</v>
-      </c>
-      <c r="T5" s="20"/>
-      <c r="U5" s="20">
-        <v>0</v>
-      </c>
-      <c r="V5" s="20">
-        <v>0</v>
-      </c>
-      <c r="W5" s="20">
-        <v>0</v>
-      </c>
-      <c r="X5" s="20">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="20">
-        <v>297380.76923076925</v>
-      </c>
-      <c r="Z5" s="20">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="20">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="20">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="20">
-        <v>0</v>
-      </c>
-      <c r="AH5" s="20">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="20">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="20">
-        <v>0</v>
-      </c>
-      <c r="AL5" s="20">
-        <v>0</v>
-      </c>
-      <c r="AN5" s="20">
-        <v>0</v>
-      </c>
-      <c r="AO5" s="20">
-        <v>0</v>
-      </c>
-      <c r="AP5" s="20">
-        <v>1</v>
-      </c>
-      <c r="AS5" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="AU5" s="20">
-        <v>744615.38461538462</v>
-      </c>
-      <c r="AV5" s="20">
-        <v>5883269.076923077</v>
-      </c>
-      <c r="AW5" s="20">
-        <v>8000000</v>
-      </c>
-      <c r="AX5" s="18">
-        <v>40000</v>
-      </c>
-      <c r="AY5" s="18">
-        <v>840000</v>
-      </c>
-      <c r="AZ5" s="20">
-        <v>0</v>
-      </c>
-      <c r="BB5" s="20">
-        <v>0</v>
-      </c>
-      <c r="BC5" s="20">
-        <v>0</v>
-      </c>
-      <c r="BD5" s="20">
-        <v>0</v>
-      </c>
-      <c r="BE5" s="20">
-        <v>0</v>
-      </c>
-      <c r="BF5" s="18">
-        <v>880000</v>
-      </c>
-      <c r="BG5" s="20">
-        <v>5003269.076923077</v>
-      </c>
-      <c r="BJ5" s="20">
-        <v>5003269.076923077</v>
-      </c>
-      <c r="BK5" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:63" ht="18" x14ac:dyDescent="0.45">
-      <c r="A6" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="F6" s="20">
-        <v>10000000</v>
-      </c>
-      <c r="G6" s="20">
-        <v>7361000</v>
-      </c>
-      <c r="H6" s="20">
-        <v>5</v>
-      </c>
-      <c r="I6" s="20">
-        <v>1415576.923076923</v>
-      </c>
-      <c r="J6" s="20">
-        <v>0</v>
-      </c>
-      <c r="K6" s="20">
-        <v>0</v>
-      </c>
-      <c r="L6" s="20">
-        <v>12.1</v>
-      </c>
-      <c r="M6" s="20">
-        <v>3425696</v>
-      </c>
-      <c r="N6" s="20">
-        <v>0</v>
-      </c>
-      <c r="O6" s="20">
-        <v>0</v>
-      </c>
-      <c r="P6" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="20">
-        <v>0</v>
-      </c>
-      <c r="R6" s="20">
-        <v>0</v>
-      </c>
-      <c r="S6" s="20">
-        <v>0</v>
-      </c>
-      <c r="T6" s="20"/>
-      <c r="U6" s="20">
-        <v>0</v>
-      </c>
-      <c r="V6" s="20">
-        <v>0</v>
-      </c>
-      <c r="W6" s="20">
-        <v>0</v>
-      </c>
-      <c r="X6" s="20">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="20">
-        <v>297380.76923076925</v>
-      </c>
-      <c r="Z6" s="20">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="20">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="20">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="20">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="20">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="20">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="20">
-        <v>0</v>
-      </c>
-      <c r="AL6" s="20">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="20">
-        <v>0</v>
-      </c>
-      <c r="AO6" s="20">
-        <v>0</v>
-      </c>
-      <c r="AP6" s="20">
-        <v>1</v>
-      </c>
-      <c r="AS6" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="AU6" s="20">
-        <v>744615.38461538462</v>
-      </c>
-      <c r="AV6" s="20">
-        <v>5883269.076923077</v>
-      </c>
-      <c r="AW6" s="20">
-        <v>8000000</v>
-      </c>
-      <c r="AX6" s="18">
-        <v>40000</v>
-      </c>
-      <c r="AY6" s="18">
-        <v>840000</v>
-      </c>
-      <c r="AZ6" s="20">
-        <v>0</v>
-      </c>
-      <c r="BB6" s="20">
-        <v>0</v>
-      </c>
-      <c r="BC6" s="20">
-        <v>0</v>
-      </c>
-      <c r="BD6" s="20">
-        <v>0</v>
-      </c>
-      <c r="BE6" s="20">
-        <v>0</v>
-      </c>
-      <c r="BF6" s="18">
-        <v>880000</v>
-      </c>
-      <c r="BG6" s="20">
-        <v>5003269.076923077</v>
-      </c>
-      <c r="BJ6" s="20">
-        <v>5003269.076923077</v>
-      </c>
-      <c r="BK6" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:63" ht="20.25" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="AN1:AS1"/>
+  </mergeCells>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <conditionalFormatting sqref="D3">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>